--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Methoden für den Nachweis von Resistenzgenen oder Resistenzmutationen (molekulare Verfahren).</t>
+    <t>Methoden für den Nachweis von Resistenzmechanismen und Determinanten: molekulare, immunologische und funktionale Verfahren.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -136,6 +136,42 @@
   </si>
   <si>
     <t>Nucleic acid sequencing technique (qualifier value)</t>
+  </si>
+  <si>
+    <t>726449005</t>
+  </si>
+  <si>
+    <t>Immunoassay technique (qualifier value)</t>
+  </si>
+  <si>
+    <t>708099001</t>
+  </si>
+  <si>
+    <t>Rapid immunoassay technique (qualifier value)</t>
+  </si>
+  <si>
+    <t>703444002</t>
+  </si>
+  <si>
+    <t>Fluorescent immunoassay (qualifier value)</t>
+  </si>
+  <si>
+    <t>708104000</t>
+  </si>
+  <si>
+    <t>Agglutination technique (qualifier value)</t>
+  </si>
+  <si>
+    <t>703458000</t>
+  </si>
+  <si>
+    <t>Neutralization method (qualifier value)</t>
+  </si>
+  <si>
+    <t>782518009</t>
+  </si>
+  <si>
+    <t>Modified carbapenem inactivation technique (qualifier value)</t>
   </si>
   <si>
     <t/>
@@ -408,7 +444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -476,15 +512,63 @@
         <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,6 +132,12 @@
     <t>Transcription mediated amplification technique (qualifier value)</t>
   </si>
   <si>
+    <t>1259932009</t>
+  </si>
+  <si>
+    <t>Loop-mediated isothermal amplification technique (qualifier value)</t>
+  </si>
+  <si>
     <t>1304162005</t>
   </si>
   <si>
@@ -172,6 +178,30 @@
   </si>
   <si>
     <t>Modified carbapenem inactivation technique (qualifier value)</t>
+  </si>
+  <si>
+    <t>1303975003</t>
+  </si>
+  <si>
+    <t>Disk diffusion technique (qualifier value)</t>
+  </si>
+  <si>
+    <t>703442003</t>
+  </si>
+  <si>
+    <t>Gradient strip susceptibility test technique (qualifier value)</t>
+  </si>
+  <si>
+    <t>260111000146108</t>
+  </si>
+  <si>
+    <t>Manual minimum inhibitory concentration microdilution susceptibility test technique (qualifier value)</t>
+  </si>
+  <si>
+    <t>260101000146106</t>
+  </si>
+  <si>
+    <t>Automated minimum inhibitory concentration microdilution susceptibility test technique (qualifier value)</t>
   </si>
   <si>
     <t/>
@@ -444,7 +474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -560,15 +590,55 @@
         <v>53</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
